--- a/JsonConverter/ExcelFiles/EnemyBattle.xlsx
+++ b/JsonConverter/ExcelFiles/EnemyBattle.xlsx
@@ -5,11 +5,11 @@
   <x:workbookPr date1904="0" showBorderUnselectedTables="1" filterPrivacy="0" promptedSolutions="0" showInkAnnotation="1" backupFile="0" saveExternalLinkValues="1" codeName="ThisWorkbook" hidePivotFieldList="0" allowRefreshQuery="0" publishItems="0" checkCompatibility="0" autoCompressPictures="1" refreshAllConnections="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\0_UnityProjects\Hero_Nursing\JsonConverter\ExcelFiles\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\NRUnityProjects\ACE\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <x:bookViews>
-    <x:workbookView xWindow="0" yWindow="0" windowWidth="22780" windowHeight="8480"/>
+    <x:workbookView xWindow="0" yWindow="0" windowWidth="28545" windowHeight="11745"/>
   </x:bookViews>
   <x:sheets>
     <x:sheet name="EnemyBattle" sheetId="1" r:id="rId4"/>
@@ -21,52 +21,16 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="19">
   <x:si>
-    <x:t>DefensePower</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MaxHp</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ID</x:t>
+    <x:t>공격력</x:t>
   </x:si>
   <x:si>
     <x:t>int</x:t>
   </x:si>
   <x:si>
-    <x:t>Speed</x:t>
-  </x:si>
-  <x:si>
-    <x:t>enemy_02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>enemy_06</x:t>
-  </x:si>
-  <x:si>
-    <x:t>enemy_04</x:t>
-  </x:si>
-  <x:si>
-    <x:t>enemy_03</x:t>
-  </x:si>
-  <x:si>
-    <x:t>enemy_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>enemy_07</x:t>
-  </x:si>
-  <x:si>
-    <x:t>enemy_05</x:t>
-  </x:si>
-  <x:si>
-    <x:t>최대 체력</x:t>
-  </x:si>
-  <x:si>
     <x:t>속도</x:t>
   </x:si>
   <x:si>
-    <x:t>공격력</x:t>
+    <x:t>ID</x:t>
   </x:si>
   <x:si>
     <x:t>적ID</x:t>
@@ -75,7 +39,43 @@
     <x:t>방어력</x:t>
   </x:si>
   <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>최대 체력</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MaxHp</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Speed</x:t>
+  </x:si>
+  <x:si>
+    <x:t>enemy_07</x:t>
+  </x:si>
+  <x:si>
+    <x:t>enemy_04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>enemy_06</x:t>
+  </x:si>
+  <x:si>
+    <x:t>enemy_05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>enemy_03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>enemy_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>enemy_01</x:t>
+  </x:si>
+  <x:si>
     <x:t>AttackPower</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DefensePower</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -892,36 +892,36 @@
   <x:sheetData>
     <x:row r="1" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A1" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="B1" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C1" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="D1" s="2" t="s">
-        <x:v>15</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E1" s="2" t="s">
-        <x:v>17</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:6" ht="13.199999999999999">
       <x:c r="A2" s="1" t="s">
-        <x:v>2</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>4</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>4</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="D2" s="1" t="s">
-        <x:v>4</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="E2" s="1" t="s">
-        <x:v>4</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="F2" s="1"/>
     </x:row>
@@ -930,34 +930,34 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B3" s="12" t="s">
-        <x:v>1</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C3" s="12" t="s">
-        <x:v>5</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="D3" s="16" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E3" s="16" t="s">
         <x:v>18</x:v>
-      </x:c>
-      <x:c r="E3" s="16" t="s">
-        <x:v>0</x:v>
       </x:c>
       <x:c r="F3" s="14"/>
     </x:row>
     <x:row r="4" spans="1:15" ht="15.75" customHeight="1">
       <x:c r="A4" s="4" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B4" s="4">
-        <x:v>100</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C4" s="4">
-        <x:v>30</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D4" s="5">
         <x:v>12</x:v>
       </x:c>
       <x:c r="E4" s="5">
-        <x:v>9</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="F4" s="15"/>
       <x:c r="G4" s="5"/>
@@ -972,19 +972,19 @@
     </x:row>
     <x:row r="5" spans="1:15" ht="15.75" customHeight="1">
       <x:c r="A5" s="4" t="s">
-        <x:v>6</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B5" s="6">
-        <x:v>90</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C5" s="6">
-        <x:v>50</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D5" s="5">
-        <x:v>8</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E5" s="5">
-        <x:v>7</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="F5" s="5"/>
       <x:c r="G5" s="5"/>
@@ -999,7 +999,7 @@
     </x:row>
     <x:row r="6" spans="1:15" ht="15.75" customHeight="1">
       <x:c r="A6" s="4" t="s">
-        <x:v>9</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B6" s="6">
         <x:v>80</x:v>
@@ -1026,7 +1026,7 @@
     </x:row>
     <x:row r="7" spans="1:15" ht="15.75" customHeight="1">
       <x:c r="A7" s="4" t="s">
-        <x:v>8</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B7" s="4">
         <x:v>85</x:v>
@@ -1053,7 +1053,7 @@
     </x:row>
     <x:row r="8" spans="1:15" ht="15.75" customHeight="1">
       <x:c r="A8" s="4" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B8" s="7">
         <x:v>95</x:v>
@@ -1080,7 +1080,7 @@
     </x:row>
     <x:row r="9" spans="1:15" ht="15.75" customHeight="1">
       <x:c r="A9" s="4" t="s">
-        <x:v>7</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="B9" s="7">
         <x:v>110</x:v>
@@ -1107,7 +1107,7 @@
     </x:row>
     <x:row r="10" spans="1:15" ht="15.75" customHeight="1">
       <x:c r="A10" s="4" t="s">
-        <x:v>11</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B10" s="1">
         <x:v>95</x:v>
@@ -2289,7 +2289,7 @@
     <x:row r="999" ht="15.75" customHeight="1"/>
     <x:row r="1000" ht="15.75" customHeight="1"/>
   </x:sheetData>
-  <x:pageMargins left="0.69986110925674438" right="0.69986110925674438" top="0.75" bottom="0.75" header="0.30000001192092896" footer="0.30000001192092896"/>
+  <x:pageMargins left="0.69972223043441772" right="0.69972223043441772" top="0.75" bottom="0.75" header="0.30000001192092896" footer="0.30000001192092896"/>
   <x:pageSetup paperSize="9" scale="100" firstPageNumber="1" fitToWidth="1" fitToHeight="1" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" useFirstPageNumber="0" horizontalDpi="600" verticalDpi="600" copies="1"/>
 </x:worksheet>
 </file>